--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ255"/>
+  <dimension ref="A1:AZ259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32364,59 +32364,48 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>54605883</v>
+        <v>136646148</v>
       </c>
       <c r="B251" t="n">
-        <v>96313</v>
+        <v>79474</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>530</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>485029</v>
+        <v>479941</v>
       </c>
       <c r="R251" t="n">
-        <v>6574808</v>
+        <v>6587258</v>
       </c>
       <c r="S251" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -32430,7 +32419,7 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
@@ -32440,12 +32429,22 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32456,92 +32455,66 @@
       </c>
       <c r="AG251" t="b">
         <v>0</v>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/136646148</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>86293398</v>
+        <v>136646260</v>
       </c>
       <c r="B252" t="n">
-        <v>110078</v>
+        <v>79474</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>220299</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>483641</v>
+        <v>479940</v>
       </c>
       <c r="R252" t="n">
-        <v>6573880</v>
+        <v>6587253</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -32558,7 +32531,7 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
@@ -32566,24 +32539,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32592,43 +32565,33 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
-      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
-        </is>
       </c>
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY252" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/136646260</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>721992</v>
+        <v>136646348</v>
       </c>
       <c r="B253" t="n">
-        <v>104211</v>
+        <v>79474</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32636,48 +32599,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1910</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Roth</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>486559</v>
+        <v>479940</v>
       </c>
       <c r="R253" t="n">
-        <v>6572552</v>
+        <v>6587248</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -32694,7 +32643,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
@@ -32702,24 +32651,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>T-Kar-0152</t>
-        </is>
-      </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>Upptäckt 2009.</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32730,40 +32679,31 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/136646348</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>125598096</v>
+        <v>136645939</v>
       </c>
       <c r="B254" t="n">
-        <v>57950</v>
+        <v>5202</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32771,16 +32711,16 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -32789,24 +32729,19 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>485667</v>
+        <v>479902</v>
       </c>
       <c r="R254" t="n">
-        <v>6572353</v>
+        <v>6587298</v>
       </c>
       <c r="S254" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -32820,7 +32755,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
@@ -32830,27 +32765,22 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Färska hack i högstubbe</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32861,53 +32791,28 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/136645939</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>54597186</v>
+        <v>54605883</v>
       </c>
       <c r="B255" t="n">
         <v>96313</v>
@@ -32942,24 +32847,24 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kärmen, Nrk</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>484632</v>
+        <v>485029</v>
       </c>
       <c r="R255" t="n">
-        <v>6571731</v>
+        <v>6574808</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -32983,12 +32888,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -33007,7 +32912,7 @@
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>sten i skyddat läge ganska nära dämmet</t>
         </is>
       </c>
       <c r="AT255" t="inlineStr"/>
@@ -33023,6 +32928,549 @@
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54605883</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>86293398</v>
+      </c>
+      <c r="B256" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Norviken, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>483641</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6573880</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Kar-0070</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+        </is>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>721992</v>
+      </c>
+      <c r="B257" t="n">
+        <v>104211</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>486559</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6572552</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Upptäckt 2009.</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+        </is>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/721992</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>125598096</v>
+      </c>
+      <c r="B258" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Kärmsön, Kärmsön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>485667</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6572353</v>
+      </c>
+      <c r="S258" t="n">
+        <v>3</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B259" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>530</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R259" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S259" t="n">
+        <v>10</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -33284,6 +33732,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ259"/>
+  <dimension ref="A1:AZ264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32364,32 +32364,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>136646148</v>
+        <v>136682855</v>
       </c>
       <c r="B251" t="n">
-        <v>79474</v>
+        <v>93441</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -32399,10 +32399,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>479941</v>
+        <v>479998</v>
       </c>
       <c r="R251" t="n">
-        <v>6587258</v>
+        <v>6587344</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -32429,22 +32429,22 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32470,13 +32470,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646148</t>
+          <t>https://artportalen.se/Sighting/136682855</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>136646260</v>
+        <v>136646148</v>
       </c>
       <c r="B252" t="n">
         <v>79474</v>
@@ -32511,10 +32511,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>479940</v>
+        <v>479941</v>
       </c>
       <c r="R252" t="n">
-        <v>6587253</v>
+        <v>6587258</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -32546,7 +32546,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -32556,7 +32556,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32582,13 +32582,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646260</t>
+          <t>https://artportalen.se/Sighting/136646148</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>136646348</v>
+        <v>136646260</v>
       </c>
       <c r="B253" t="n">
         <v>79474</v>
@@ -32626,7 +32626,7 @@
         <v>479940</v>
       </c>
       <c r="R253" t="n">
-        <v>6587248</v>
+        <v>6587253</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -32658,7 +32658,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32694,38 +32694,38 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646348</t>
+          <t>https://artportalen.se/Sighting/136646260</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>136645939</v>
+        <v>136646348</v>
       </c>
       <c r="B254" t="n">
-        <v>5202</v>
+        <v>79474</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -32735,10 +32735,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>479902</v>
+        <v>479940</v>
       </c>
       <c r="R254" t="n">
-        <v>6587298</v>
+        <v>6587248</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -32770,7 +32770,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -32780,7 +32780,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32806,65 +32806,54 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136645939</t>
+          <t>https://artportalen.se/Sighting/136646348</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>54605883</v>
+        <v>136684518</v>
       </c>
       <c r="B255" t="n">
-        <v>96313</v>
+        <v>79474</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>530</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>485029</v>
+        <v>479850</v>
       </c>
       <c r="R255" t="n">
-        <v>6574808</v>
+        <v>6587467</v>
       </c>
       <c r="S255" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -32878,7 +32867,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
@@ -32888,12 +32877,27 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Kraftigt exemplar.</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -32904,41 +32908,31 @@
       </c>
       <c r="AG255" t="b">
         <v>0</v>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/136684518</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>86293398</v>
+        <v>136682570</v>
       </c>
       <c r="B256" t="n">
-        <v>110078</v>
+        <v>79560</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32946,50 +32940,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>220299</v>
+        <v>6450</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>483641</v>
+        <v>479940</v>
       </c>
       <c r="R256" t="n">
-        <v>6573880</v>
+        <v>6587255</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -33006,7 +32984,7 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
@@ -33014,24 +32992,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -33040,92 +33018,82 @@
       <c r="AE256" t="b">
         <v>0</v>
       </c>
-      <c r="AF256" t="inlineStr"/>
       <c r="AG256" t="b">
         <v>0</v>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
-        </is>
       </c>
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY256" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/136682570</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>721992</v>
+        <v>136684353</v>
       </c>
       <c r="B257" t="n">
-        <v>104211</v>
+        <v>58006</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1910</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>486559</v>
+        <v>479911</v>
       </c>
       <c r="R257" t="n">
-        <v>6572552</v>
+        <v>6587498</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -33142,7 +33110,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
@@ -33150,24 +33118,29 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>T-Kar-0152</t>
-        </is>
-      </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Upptäckt 2009.</t>
+          <t>Kraftiga ringbarkningar i tall.</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -33178,83 +33151,83 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
-        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY257" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/136684353</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>125598096</v>
+        <v>136683251</v>
       </c>
       <c r="B258" t="n">
-        <v>57950</v>
+        <v>58167</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>485667</v>
+        <v>480003</v>
       </c>
       <c r="R258" t="n">
-        <v>6572353</v>
+        <v>6587469</v>
       </c>
       <c r="S258" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -33268,7 +33241,7 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
@@ -33278,27 +33251,27 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Färska hack i högstubbe</t>
+          <t>Upprörd, varnande.</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -33309,56 +33282,31 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/136683251</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>54597186</v>
+        <v>136645939</v>
       </c>
       <c r="B259" t="n">
-        <v>96313</v>
+        <v>5202</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33366,45 +33314,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>530</v>
+        <v>105930</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>484632</v>
+        <v>479902</v>
       </c>
       <c r="R259" t="n">
-        <v>6571731</v>
+        <v>6587298</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -33421,7 +33358,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
@@ -33431,12 +33368,22 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -33447,30 +33394,686 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136645939</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>54605883</v>
+      </c>
+      <c r="B260" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>530</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Kärmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>485029</v>
+      </c>
+      <c r="R260" t="n">
+        <v>6574808</v>
+      </c>
+      <c r="S260" t="n">
+        <v>25</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2015-07-16</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2015-07-16</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>sten i skyddat läge ganska nära dämmet</t>
+        </is>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54605883</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>86293398</v>
+      </c>
+      <c r="B261" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Norviken, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>483641</v>
+      </c>
+      <c r="R261" t="n">
+        <v>6573880</v>
+      </c>
+      <c r="S261" t="n">
+        <v>10</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Kar-0070</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+        </is>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>721992</v>
+      </c>
+      <c r="B262" t="n">
+        <v>104211</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>486559</v>
+      </c>
+      <c r="R262" t="n">
+        <v>6572552</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Upptäckt 2009.</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+        </is>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/721992</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>125598096</v>
+      </c>
+      <c r="B263" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Kärmsön, Kärmsön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>485667</v>
+      </c>
+      <c r="R263" t="n">
+        <v>6572353</v>
+      </c>
+      <c r="S263" t="n">
+        <v>3</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B264" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>530</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R264" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S264" t="n">
+        <v>10</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -33736,6 +34339,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136682855</v>
       </c>
       <c r="B251" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ264"/>
+  <dimension ref="A1:AZ265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32364,32 +32364,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>136682855</v>
+        <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>93442</v>
+        <v>92074</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -32399,10 +32399,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>479998</v>
+        <v>479889</v>
       </c>
       <c r="R251" t="n">
-        <v>6587344</v>
+        <v>6587393</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -32429,22 +32429,22 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32470,38 +32470,38 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136682855</t>
+          <t>https://artportalen.se/Sighting/136763880</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>136646148</v>
+        <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>79474</v>
+        <v>93447</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -32511,10 +32511,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>479941</v>
+        <v>479998</v>
       </c>
       <c r="R252" t="n">
-        <v>6587258</v>
+        <v>6587344</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -32541,22 +32541,22 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32582,16 +32582,16 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646148</t>
+          <t>https://artportalen.se/Sighting/136682855</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>136646260</v>
+        <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32623,10 +32623,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>479940</v>
+        <v>479941</v>
       </c>
       <c r="R253" t="n">
-        <v>6587253</v>
+        <v>6587258</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -32658,7 +32658,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32694,16 +32694,16 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646260</t>
+          <t>https://artportalen.se/Sighting/136646148</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>136646348</v>
+        <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>479940</v>
       </c>
       <c r="R254" t="n">
-        <v>6587248</v>
+        <v>6587253</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -32770,7 +32770,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -32780,7 +32780,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32806,16 +32806,16 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646348</t>
+          <t>https://artportalen.se/Sighting/136646260</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>136684518</v>
+        <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32843,14 +32843,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>479850</v>
+        <v>479940</v>
       </c>
       <c r="R255" t="n">
-        <v>6587467</v>
+        <v>6587248</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -32877,27 +32877,22 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Kraftigt exemplar.</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -32923,51 +32918,51 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136684518</t>
+          <t>https://artportalen.se/Sighting/136646348</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>136682570</v>
+        <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79560</v>
+        <v>79476</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>479940</v>
+        <v>479850</v>
       </c>
       <c r="R256" t="n">
-        <v>6587255</v>
+        <v>6587467</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -32999,7 +32994,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -33009,7 +33004,12 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Kraftigt exemplar.</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -33035,16 +33035,16 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136682570</t>
+          <t>https://artportalen.se/Sighting/136684518</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>136684353</v>
+        <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>58006</v>
+        <v>79562</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33052,48 +33052,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>479911</v>
+        <v>479940</v>
       </c>
       <c r="R257" t="n">
-        <v>6587498</v>
+        <v>6587255</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -33125,7 +33111,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -33135,12 +33121,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Kraftiga ringbarkningar i tall.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -33166,16 +33147,16 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136684353</t>
+          <t>https://artportalen.se/Sighting/136682570</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>136683251</v>
+        <v>136684353</v>
       </c>
       <c r="B258" t="n">
-        <v>58167</v>
+        <v>58008</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33183,21 +33164,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -33212,19 +33193,19 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>480003</v>
+        <v>479911</v>
       </c>
       <c r="R258" t="n">
-        <v>6587469</v>
+        <v>6587498</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -33256,7 +33237,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -33266,12 +33247,12 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Upprörd, varnande.</t>
+          <t>Kraftiga ringbarkningar i tall.</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -33297,51 +33278,65 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136683251</t>
+          <t>https://artportalen.se/Sighting/136684353</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>136645939</v>
+        <v>136683251</v>
       </c>
       <c r="B259" t="n">
-        <v>5202</v>
+        <v>58169</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>479902</v>
+        <v>480003</v>
       </c>
       <c r="R259" t="n">
-        <v>6587298</v>
+        <v>6587469</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -33368,22 +33363,27 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -33409,16 +33409,16 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136645939</t>
+          <t>https://artportalen.se/Sighting/136683251</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>54605883</v>
+        <v>136645939</v>
       </c>
       <c r="B260" t="n">
-        <v>96313</v>
+        <v>5202</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33426,48 +33426,37 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>530</v>
+        <v>105930</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>485029</v>
+        <v>479902</v>
       </c>
       <c r="R260" t="n">
-        <v>6574808</v>
+        <v>6587298</v>
       </c>
       <c r="S260" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -33481,7 +33470,7 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
@@ -33491,12 +33480,22 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -33507,95 +33506,80 @@
       </c>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/136645939</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>86293398</v>
+        <v>54605883</v>
       </c>
       <c r="B261" t="n">
-        <v>110078</v>
+        <v>96313</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>220299</v>
+        <v>530</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kärmen, Nrk</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>483641</v>
+        <v>485029</v>
       </c>
       <c r="R261" t="n">
-        <v>6573880</v>
+        <v>6574808</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -33617,24 +33601,14 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -33643,70 +33617,70 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>sten i skyddat läge ganska nära dämmet</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY261" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/54605883</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>721992</v>
+        <v>86293398</v>
       </c>
       <c r="B262" t="n">
-        <v>104211</v>
+        <v>110078</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1910</v>
+        <v>220299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -33719,16 +33693,18 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Norviken, V om, Nrk</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>486559</v>
+        <v>483641</v>
       </c>
       <c r="R262" t="n">
-        <v>6572552</v>
+        <v>6573880</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -33755,22 +33731,22 @@
       </c>
       <c r="X262" t="inlineStr">
         <is>
-          <t>T-Kar-0152</t>
+          <t>Arkiv-T-Kar-0070</t>
         </is>
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Upptäckt 2009.</t>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -33779,12 +33755,13 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -33800,64 +33777,73 @@
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/86293398</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>125598096</v>
+        <v>721992</v>
       </c>
       <c r="B263" t="n">
-        <v>57950</v>
+        <v>104211</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100049</v>
+        <v>1910</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>485667</v>
+        <v>486559</v>
       </c>
       <c r="R263" t="n">
-        <v>6572353</v>
+        <v>6572552</v>
       </c>
       <c r="S263" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -33879,29 +33865,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Färska hack i högstubbe</t>
+          <t>Upptäckt 2009.</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -33913,55 +33894,39 @@
       <c r="AG263" t="b">
         <v>0</v>
       </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
         </is>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY263" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/721992</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>54597186</v>
+        <v>125598096</v>
       </c>
       <c r="B264" t="n">
-        <v>96313</v>
+        <v>57950</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -33969,48 +33934,42 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>530</v>
+        <v>100049</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kärmsön, Kärmsön, Nrk</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>484632</v>
+        <v>485667</v>
       </c>
       <c r="R264" t="n">
-        <v>6571731</v>
+        <v>6572353</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -34034,12 +33993,27 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -34051,29 +34025,167 @@
       <c r="AG264" t="b">
         <v>0</v>
       </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B265" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>530</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R265" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -34344,6 +34456,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79566</v>
+        <v>79568</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ265"/>
+  <dimension ref="A1:AZ290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33153,27 +33153,27 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>136684353</v>
+        <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -33191,21 +33191,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>479911</v>
+        <v>480001</v>
       </c>
       <c r="R258" t="n">
-        <v>6587498</v>
+        <v>6587388</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -33232,27 +33234,27 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Kraftiga ringbarkningar i tall.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -33278,38 +33280,38 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136684353</t>
+          <t>https://artportalen.se/Sighting/137195400</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>136683251</v>
+        <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -33322,21 +33324,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>480003</v>
+        <v>479966</v>
       </c>
       <c r="R259" t="n">
-        <v>6587469</v>
+        <v>6587394</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -33363,27 +33367,27 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Upprörd, varnande.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -33409,16 +33413,16 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136683251</t>
+          <t>https://artportalen.se/Sighting/137195419</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>136645939</v>
+        <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>5202</v>
+        <v>58005</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33426,16 +33430,16 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -33443,17 +33447,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>479902</v>
+        <v>479992</v>
       </c>
       <c r="R260" t="n">
-        <v>6587298</v>
+        <v>6587411</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -33480,22 +33500,27 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -33521,16 +33546,16 @@
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136645939</t>
+          <t>https://artportalen.se/Sighting/137195464</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>54605883</v>
+        <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>96313</v>
+        <v>58005</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33538,48 +33563,53 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>530</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>485029</v>
+        <v>479920</v>
       </c>
       <c r="R261" t="n">
-        <v>6574808</v>
+        <v>6587403</v>
       </c>
       <c r="S261" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -33593,7 +33623,7 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
@@ -33603,12 +33633,27 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -33619,92 +33664,82 @@
       </c>
       <c r="AG261" t="b">
         <v>0</v>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO261" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/137195484</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>86293398</v>
+        <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>110078</v>
+        <v>58005</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>483641</v>
+        <v>479978</v>
       </c>
       <c r="R262" t="n">
-        <v>6573880</v>
+        <v>6587366</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -33721,7 +33756,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W262" t="inlineStr">
@@ -33729,24 +33764,29 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -33755,92 +33795,84 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
-        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/137195526</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>721992</v>
+        <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>104211</v>
+        <v>58005</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1910</v>
+        <v>100049</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>486559</v>
+        <v>479991</v>
       </c>
       <c r="R263" t="n">
-        <v>6572552</v>
+        <v>6587357</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -33857,7 +33889,7 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
@@ -33865,24 +33897,29 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>T-Kar-0152</t>
-        </is>
-      </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Upptäckt 2009.</t>
+          <t>Spel/sång,</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -33893,40 +33930,31 @@
       </c>
       <c r="AG263" t="b">
         <v>0</v>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
-        </is>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY263" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/137195571</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>125598096</v>
+        <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>57950</v>
+        <v>58005</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -33951,25 +33979,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>485667</v>
+        <v>480006</v>
       </c>
       <c r="R264" t="n">
-        <v>6572353</v>
+        <v>6587369</v>
       </c>
       <c r="S264" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -33983,7 +34022,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W264" t="inlineStr">
@@ -33993,27 +34032,27 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Färska hack i högstubbe</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -34024,102 +34063,82 @@
       </c>
       <c r="AG264" t="b">
         <v>0</v>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/137195577</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>54597186</v>
+        <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>96313</v>
+        <v>58122</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>530</v>
+        <v>100090</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kalvtjärnshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>484632</v>
+        <v>479958</v>
       </c>
       <c r="R265" t="n">
-        <v>6571731</v>
+        <v>6587362</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -34136,7 +34155,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W265" t="inlineStr">
@@ -34146,12 +34165,22 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -34162,30 +34191,3281 @@
       </c>
       <c r="AG265" t="b">
         <v>0</v>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195105</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>136684353</v>
+      </c>
+      <c r="B266" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>479911</v>
+      </c>
+      <c r="R266" t="n">
+        <v>6587498</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>Kraftiga ringbarkningar i tall.</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136684353</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>137194805</v>
+      </c>
+      <c r="B267" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>479932</v>
+      </c>
+      <c r="R267" t="n">
+        <v>6587422</v>
+      </c>
+      <c r="S267" t="n">
+        <v>10</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137194805</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>137194884</v>
+      </c>
+      <c r="B268" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>479949</v>
+      </c>
+      <c r="R268" t="n">
+        <v>6587435</v>
+      </c>
+      <c r="S268" t="n">
+        <v>10</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137194884</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>137194988</v>
+      </c>
+      <c r="B269" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>479952</v>
+      </c>
+      <c r="R269" t="n">
+        <v>6587418</v>
+      </c>
+      <c r="S269" t="n">
+        <v>10</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137194988</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>137195004</v>
+      </c>
+      <c r="B270" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>479941</v>
+      </c>
+      <c r="R270" t="n">
+        <v>6587407</v>
+      </c>
+      <c r="S270" t="n">
+        <v>10</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195004</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>137195023</v>
+      </c>
+      <c r="B271" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>479960</v>
+      </c>
+      <c r="R271" t="n">
+        <v>6587403</v>
+      </c>
+      <c r="S271" t="n">
+        <v>10</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195023</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>137195036</v>
+      </c>
+      <c r="B272" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>479972</v>
+      </c>
+      <c r="R272" t="n">
+        <v>6587416</v>
+      </c>
+      <c r="S272" t="n">
+        <v>10</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195036</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>137195046</v>
+      </c>
+      <c r="B273" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>479980</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6587397</v>
+      </c>
+      <c r="S273" t="n">
+        <v>10</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195046</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>137195062</v>
+      </c>
+      <c r="B274" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>479951</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6587390</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195062</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>137195068</v>
+      </c>
+      <c r="B275" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>479970</v>
+      </c>
+      <c r="R275" t="n">
+        <v>6587383</v>
+      </c>
+      <c r="S275" t="n">
+        <v>10</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195068</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>137195249</v>
+      </c>
+      <c r="B276" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>479950</v>
+      </c>
+      <c r="R276" t="n">
+        <v>6587372</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195249</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>137195167</v>
+      </c>
+      <c r="B277" t="n">
+        <v>57840</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>479988</v>
+      </c>
+      <c r="R277" t="n">
+        <v>6587370</v>
+      </c>
+      <c r="S277" t="n">
+        <v>10</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Lockläte, övriga läten.</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195167</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>137195203</v>
+      </c>
+      <c r="B278" t="n">
+        <v>57840</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>479930</v>
+      </c>
+      <c r="R278" t="n">
+        <v>6587390</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>01:04</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>01:04</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>Lockläte, övriga läten.</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195203</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>136683251</v>
+      </c>
+      <c r="B279" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>480003</v>
+      </c>
+      <c r="R279" t="n">
+        <v>6587469</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande.</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683251</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>137195604</v>
+      </c>
+      <c r="B280" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>479990</v>
+      </c>
+      <c r="R280" t="n">
+        <v>6587346</v>
+      </c>
+      <c r="S280" t="n">
+        <v>10</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>Spel/sång,</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195604</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>137195645</v>
+      </c>
+      <c r="B281" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>479937</v>
+      </c>
+      <c r="R281" t="n">
+        <v>6587373</v>
+      </c>
+      <c r="S281" t="n">
+        <v>10</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195645</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>137195662</v>
+      </c>
+      <c r="B282" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>479973</v>
+      </c>
+      <c r="R282" t="n">
+        <v>6587437</v>
+      </c>
+      <c r="S282" t="n">
+        <v>10</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195662</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>137195669</v>
+      </c>
+      <c r="B283" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>479990</v>
+      </c>
+      <c r="R283" t="n">
+        <v>6587431</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195669</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>137195691</v>
+      </c>
+      <c r="B284" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Kalvtjärnshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>480003</v>
+      </c>
+      <c r="R284" t="n">
+        <v>6587402</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195691</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>136645939</v>
+      </c>
+      <c r="B285" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Kalvtjärn, Kalvtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>479902</v>
+      </c>
+      <c r="R285" t="n">
+        <v>6587298</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136645939</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>54605883</v>
+      </c>
+      <c r="B286" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>530</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Kärmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>485029</v>
+      </c>
+      <c r="R286" t="n">
+        <v>6574808</v>
+      </c>
+      <c r="S286" t="n">
+        <v>25</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2015-07-16</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2015-07-16</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>sten i skyddat läge ganska nära dämmet</t>
+        </is>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54605883</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>86293398</v>
+      </c>
+      <c r="B287" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Norviken, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>483641</v>
+      </c>
+      <c r="R287" t="n">
+        <v>6573880</v>
+      </c>
+      <c r="S287" t="n">
+        <v>10</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Kar-0070</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+        </is>
+      </c>
+      <c r="AD287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+        </is>
+      </c>
+      <c r="AT287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86293398</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>721992</v>
+      </c>
+      <c r="B288" t="n">
+        <v>104211</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>486559</v>
+      </c>
+      <c r="R288" t="n">
+        <v>6572552</v>
+      </c>
+      <c r="S288" t="n">
+        <v>10</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2009-07-28</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>Upptäckt 2009.</t>
+        </is>
+      </c>
+      <c r="AD288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+        </is>
+      </c>
+      <c r="AT288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/721992</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>125598096</v>
+      </c>
+      <c r="B289" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Kärmsön, Kärmsön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>485667</v>
+      </c>
+      <c r="R289" t="n">
+        <v>6572353</v>
+      </c>
+      <c r="S289" t="n">
+        <v>3</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM289" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B290" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>530</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R290" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S290" t="n">
+        <v>10</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -34457,6 +37737,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79571</v>
+        <v>79574</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79574</v>
+        <v>79587</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>136684353</v>
       </c>
       <c r="B266" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>137194805</v>
       </c>
       <c r="B267" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>137194884</v>
       </c>
       <c r="B268" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>137194988</v>
       </c>
       <c r="B269" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>137195004</v>
       </c>
       <c r="B270" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>137195023</v>
       </c>
       <c r="B271" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>137195036</v>
       </c>
       <c r="B272" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>137195046</v>
       </c>
       <c r="B273" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>137195062</v>
       </c>
       <c r="B274" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>137195068</v>
       </c>
       <c r="B275" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57849</v>
+        <v>57862</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>137195167</v>
       </c>
       <c r="B277" t="n">
-        <v>57840</v>
+        <v>57853</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>137195203</v>
       </c>
       <c r="B278" t="n">
-        <v>57840</v>
+        <v>57853</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>136683251</v>
       </c>
       <c r="B279" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>136646148</v>
       </c>
       <c r="B253" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>136646260</v>
       </c>
       <c r="B254" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>136646348</v>
       </c>
       <c r="B255" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>136684518</v>
       </c>
       <c r="B256" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>136682570</v>
       </c>
       <c r="B257" t="n">
-        <v>79587</v>
+        <v>79589</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>136684353</v>
       </c>
       <c r="B266" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>137194805</v>
       </c>
       <c r="B267" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>137194884</v>
       </c>
       <c r="B268" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>137194988</v>
       </c>
       <c r="B269" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>137195004</v>
       </c>
       <c r="B270" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>137195023</v>
       </c>
       <c r="B271" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>137195036</v>
       </c>
       <c r="B272" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>137195046</v>
       </c>
       <c r="B273" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>137195062</v>
       </c>
       <c r="B274" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>137195068</v>
       </c>
       <c r="B275" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57862</v>
+        <v>57864</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>137195167</v>
       </c>
       <c r="B277" t="n">
-        <v>57853</v>
+        <v>57855</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>137195203</v>
       </c>
       <c r="B278" t="n">
-        <v>57853</v>
+        <v>57855</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>136683251</v>
       </c>
       <c r="B279" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -33186,17 +33186,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
@@ -33319,17 +33311,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
@@ -33452,17 +33436,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
@@ -33585,17 +33561,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
@@ -33718,17 +33686,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
@@ -33851,17 +33811,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
@@ -33984,17 +33936,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -34117,17 +34061,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -34245,16 +34181,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Ängsmossetjärnarnas naturreservat, Ängsmossetjärnarnas naturreservat, Vrm</t>
@@ -34376,17 +34304,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
@@ -34511,11 +34431,7 @@
       </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
@@ -34640,11 +34556,7 @@
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
@@ -34769,11 +34681,7 @@
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
@@ -34898,11 +34806,7 @@
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
@@ -35027,11 +34931,7 @@
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
@@ -35156,11 +35056,7 @@
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
@@ -35285,11 +35181,7 @@
       </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
@@ -35414,11 +35306,7 @@
       </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
@@ -35541,17 +35429,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
@@ -35676,11 +35556,7 @@
       </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
@@ -35805,11 +35681,7 @@
       </c>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
@@ -35932,16 +35804,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Kalvtjärn, Kalvtjärn, Vrm</t>
@@ -36063,17 +35927,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
@@ -36196,17 +36052,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
@@ -36329,17 +36177,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
@@ -36462,17 +36302,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
@@ -36595,17 +36427,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>136682855</v>
       </c>
       <c r="B252" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>137194805</v>
       </c>
       <c r="B267" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>137194884</v>
       </c>
       <c r="B268" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>137194988</v>
       </c>
       <c r="B269" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>137195004</v>
       </c>
       <c r="B270" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>137195023</v>
       </c>
       <c r="B271" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>137195036</v>
       </c>
       <c r="B272" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>137195046</v>
       </c>
       <c r="B273" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>137195062</v>
       </c>
       <c r="B274" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>137195068</v>
       </c>
       <c r="B275" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>137195167</v>
       </c>
       <c r="B277" t="n">
-        <v>57855</v>
+        <v>57865</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>137195203</v>
       </c>
       <c r="B278" t="n">
-        <v>57855</v>
+        <v>57865</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>137194805</v>
       </c>
       <c r="B267" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>137194884</v>
       </c>
       <c r="B268" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>137194988</v>
       </c>
       <c r="B269" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>137195004</v>
       </c>
       <c r="B270" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>137195023</v>
       </c>
       <c r="B271" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>137195036</v>
       </c>
       <c r="B272" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>137195046</v>
       </c>
       <c r="B273" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>137195062</v>
       </c>
       <c r="B274" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>137195068</v>
       </c>
       <c r="B275" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>137195167</v>
       </c>
       <c r="B277" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>137195203</v>
       </c>
       <c r="B278" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -32367,7 +32367,7 @@
         <v>136763880</v>
       </c>
       <c r="B251" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -33156,7 +33156,7 @@
         <v>137195400</v>
       </c>
       <c r="B258" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>137195419</v>
       </c>
       <c r="B259" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>137195464</v>
       </c>
       <c r="B260" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>137195484</v>
       </c>
       <c r="B261" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>137195526</v>
       </c>
       <c r="B262" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>137195571</v>
       </c>
       <c r="B263" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>137195577</v>
       </c>
       <c r="B264" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>137195105</v>
       </c>
       <c r="B265" t="n">
-        <v>58149</v>
+        <v>58152</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>137194805</v>
       </c>
       <c r="B267" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>137194884</v>
       </c>
       <c r="B268" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>137194988</v>
       </c>
       <c r="B269" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>137195004</v>
       </c>
       <c r="B270" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>137195023</v>
       </c>
       <c r="B271" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>137195036</v>
       </c>
       <c r="B272" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>137195046</v>
       </c>
       <c r="B273" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>137195062</v>
       </c>
       <c r="B274" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>137195068</v>
       </c>
       <c r="B275" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>137195249</v>
       </c>
       <c r="B276" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>137195167</v>
       </c>
       <c r="B277" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>137195203</v>
       </c>
       <c r="B278" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>137195604</v>
       </c>
       <c r="B280" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>137195645</v>
       </c>
       <c r="B281" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>137195662</v>
       </c>
       <c r="B282" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>137195669</v>
       </c>
       <c r="B283" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>137195691</v>
       </c>
       <c r="B284" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
